--- a/work_with_prepared_data/datas/control/16.03.2023_n_22.xlsx
+++ b/work_with_prepared_data/datas/control/16.03.2023_n_22.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Scripts\neuro_stats\work_with_prepared_data\datas\control\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\neuro_stats\work_with_prepared_data\datas\control\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94A9683D-1E73-475A-92D6-48C93B4CD4ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="15555" windowHeight="11610"/>
+    <workbookView xWindow="4710" yWindow="4770" windowWidth="19005" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table n°1" sheetId="1" r:id="rId1"/>
@@ -19,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="69">
   <si>
     <t>1,7 - 1,5 - 0,8</t>
   </si>
@@ -156,15 +157,9 @@
     <t>1,5 - 1,3 - 0,6</t>
   </si>
   <si>
-    <t>4,9 - 1,7 - 0,8</t>
-  </si>
-  <si>
     <t>1,7 - 1,3 - 0,7</t>
   </si>
   <si>
-    <t>4,8 - 1,7 - 0,9</t>
-  </si>
-  <si>
     <t>1,7 - 1,5 - 0,7</t>
   </si>
   <si>
@@ -232,15 +227,12 @@
   </si>
   <si>
     <t>2,0 -1,5 - 0,8</t>
-  </si>
-  <si>
-    <t>2,2 - 2,1 - 1,9</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -573,7 +565,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -597,7 +589,7 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B2" t="s">
         <v>12</v>
@@ -635,7 +627,7 @@
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B3" t="s">
         <v>13</v>
@@ -662,24 +654,24 @@
         <v>31</v>
       </c>
       <c r="J3" t="s">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="K3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="L3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D4" t="s">
         <v>22</v>
@@ -700,18 +692,18 @@
         <v>44</v>
       </c>
       <c r="J4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="K4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="L4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B5" t="s">
         <v>15</v>
@@ -738,18 +730,18 @@
         <v>29</v>
       </c>
       <c r="J5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="K5" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="L5" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B6" t="s">
         <v>0</v>
@@ -773,21 +765,21 @@
         <v>42</v>
       </c>
       <c r="I6" t="s">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="J6" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="K6" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="L6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B7" t="s">
         <v>16</v>
@@ -814,18 +806,18 @@
         <v>16</v>
       </c>
       <c r="J7" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="K7" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="L7" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B8" t="s">
         <v>16</v>
@@ -849,16 +841,16 @@
         <v>43</v>
       </c>
       <c r="I8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J8" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="K8" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="L8" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
